--- a/i_test/test_D3_coorte_con_caratterizzazione/med_cardioisc_angi.xlsx
+++ b/i_test/test_D3_coorte_con_caratterizzazione/med_cardioisc_angi.xlsx
@@ -20,12 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
   <si>
     <t xml:space="preserve">DATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table_cdm</t>
   </si>
   <si>
     <t xml:space="preserve">P04</t>
@@ -115,13 +118,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -141,7 +148,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -151,28 +158,31 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>2</v>
+      <c r="A2" s="2" t="s">
+        <v>3</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="2" t="n">
         <v>2900</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>3</v>
+      <c r="A3" s="2" t="s">
+        <v>4</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>3</v>
+      <c r="A4" s="2" t="s">
+        <v>4</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="2" t="n">
         <v>-729</v>
       </c>
     </row>
